--- a/data/trans_dic/P1402-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1402-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 13,75</t>
+          <t>9,89; 13,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,25; 20,13</t>
+          <t>15,18; 20,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,29; 23,25</t>
+          <t>17,2; 22,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,64; 22,56</t>
+          <t>16,06; 21,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,41; 16,1</t>
+          <t>12,4; 16,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,11; 20,49</t>
+          <t>16,3; 20,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,09; 22,51</t>
+          <t>17,17; 22,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,92; 23,04</t>
+          <t>18,78; 22,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,85; 14,64</t>
+          <t>11,95; 14,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,24; 19,54</t>
+          <t>16,58; 19,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,81; 21,78</t>
+          <t>17,84; 21,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,82; 22,38</t>
+          <t>18,27; 21,64</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,06</t>
+          <t>2,24; 3,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,75</t>
+          <t>2,99; 4,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 7,18</t>
+          <t>4,99; 7,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 8,21</t>
+          <t>6,65; 8,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,96</t>
+          <t>1,44; 2,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,06</t>
+          <t>2,31; 4,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,38</t>
+          <t>3,35; 5,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,73</t>
+          <t>3,94; 5,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,1</t>
+          <t>2,01; 3,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,14</t>
+          <t>2,85; 4,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 5,87</t>
+          <t>4,47; 5,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,22</t>
+          <t>5,53; 6,75</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,87</t>
+          <t>1,24; 4,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,85</t>
+          <t>1,4; 4,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,07</t>
+          <t>2,76; 6,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,85</t>
+          <t>5,27; 9,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,47</t>
+          <t>0,82; 3,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,27</t>
+          <t>0,65; 3,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,36</t>
+          <t>1,5; 4,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,84</t>
+          <t>1,97; 3,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,22</t>
+          <t>1,31; 3,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,3</t>
+          <t>1,27; 3,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,85</t>
+          <t>2,45; 5,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,93</t>
+          <t>3,87; 6,03</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,43</t>
+          <t>4,98; 6,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 8,53</t>
+          <t>6,56; 8,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 9,76</t>
+          <t>7,9; 9,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 9,79</t>
+          <t>8,46; 10,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 7,66</t>
+          <t>5,96; 7,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 9,65</t>
+          <t>7,64; 9,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,42</t>
+          <t>7,46; 9,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 8,08</t>
+          <t>7,19; 8,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 6,85</t>
+          <t>5,68; 6,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 8,73</t>
+          <t>7,46; 8,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,92; 9,29</t>
+          <t>8,01; 9,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 8,69</t>
+          <t>8,0; 9,1</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100149</t>
+          <t>108030</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>157625</t>
+          <t>171071</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>257774</t>
+          <t>279102</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>101437; 141874</t>
+          <t>102070; 144173</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>148640; 196161</t>
+          <t>147949; 196685</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130410; 175377</t>
+          <t>129744; 170985</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85298; 115609</t>
+          <t>92498; 125409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>163218; 211750</t>
+          <t>163080; 216321</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>215460; 274161</t>
+          <t>218117; 273603</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>170027; 223907</t>
+          <t>170805; 225009</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>142352; 173424</t>
+          <t>154086; 187775</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>278196; 343690</t>
+          <t>280535; 343340</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>375594; 451768</t>
+          <t>383360; 456384</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>311558; 380974</t>
+          <t>312071; 381403</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>238141; 283128</t>
+          <t>255167; 302183</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155737</t>
+          <t>169777</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87741</t>
+          <t>98867</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>243478</t>
+          <t>268644</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37481; 68742</t>
+          <t>37879; 65447</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58171; 93252</t>
+          <t>58651; 93031</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>103045; 148999</t>
+          <t>103567; 147605</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>109661; 187513</t>
+          <t>147872; 193379</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22602; 46931</t>
+          <t>22898; 45056</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41294; 71313</t>
+          <t>40566; 70855</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66631; 106906</t>
+          <t>66686; 106380</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63221; 105814</t>
+          <t>85548; 114417</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66526; 101875</t>
+          <t>65786; 105047</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>109595; 154099</t>
+          <t>105868; 152863</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>180539; 238759</t>
+          <t>181562; 239508</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>196401; 281302</t>
+          <t>243211; 296825</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43362</t>
+          <t>49685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>21207</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61226</t>
+          <t>70892</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6753; 21336</t>
+          <t>6821; 22769</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6792; 23323</t>
+          <t>6758; 22505</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15300; 38683</t>
+          <t>15092; 37389</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32429; 57230</t>
+          <t>37516; 64784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3448; 16510</t>
+          <t>3890; 15237</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2974; 14975</t>
+          <t>2970; 15073</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7462; 23919</t>
+          <t>8219; 23001</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12885; 25334</t>
+          <t>14475; 29262</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13893; 33079</t>
+          <t>13442; 31267</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11964; 31058</t>
+          <t>11971; 31921</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26715; 53211</t>
+          <t>26806; 54870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50576; 77477</t>
+          <t>55922; 87239</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299249</t>
+          <t>327493</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>263229</t>
+          <t>291145</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>562478</t>
+          <t>618638</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>161041; 210802</t>
+          <t>163060; 212361</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>226570; 291724</t>
+          <t>224177; 287151</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>265638; 329530</t>
+          <t>266690; 333655</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>231941; 337247</t>
+          <t>297294; 358773</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>201167; 258756</t>
+          <t>201539; 255318</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>274832; 342613</t>
+          <t>271121; 341697</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>263054; 332564</t>
+          <t>263632; 334796</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>223026; 294703</t>
+          <t>267861; 315974</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>380100; 455760</t>
+          <t>377762; 457589</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>524188; 608311</t>
+          <t>520162; 614191</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>547114; 642085</t>
+          <t>553172; 648791</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>483054; 616219</t>
+          <t>579007; 658292</t>
         </is>
       </c>
     </row>
